--- a/Balance.xlsx
+++ b/Balance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SecretHistoriesBoardGame\secret-histories\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA1862C-82BF-44E1-83A3-D1E250773913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6847E99-4B81-47C8-8B3B-9D25CBBA4489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lantern victory" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="79">
   <si>
     <t>Lore</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Influence</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Ascension</t>
@@ -383,9 +380,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
@@ -393,10 +387,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="4"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="4"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Accent3" xfId="3" builtinId="37"/>
@@ -703,7 +700,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -742,10 +739,10 @@
       <c r="F3">
         <v>2</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="8">
+      <c r="I3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="7">
         <v>2</v>
       </c>
       <c r="M3">
@@ -753,22 +750,22 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="8">
+      <c r="I4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="7">
         <v>2</v>
       </c>
     </row>
@@ -785,18 +782,18 @@
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="8">
+      <c r="I5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5">
+      <c r="A6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
         <v>2</v>
       </c>
       <c r="E6" t="s">
@@ -805,11 +802,11 @@
       <c r="F6">
         <v>8</v>
       </c>
-      <c r="I6" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
+      <c r="I6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -825,6 +822,12 @@
       <c r="F7">
         <v>8</v>
       </c>
+      <c r="I7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -834,17 +837,17 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4"/>
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -863,10 +866,10 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>4</v>
       </c>
     </row>
@@ -879,48 +882,48 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="5">
+      <c r="A14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4"/>
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="5">
+      <c r="A17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="5">
+      <c r="A18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4"/>
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="3"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -965,7 +968,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1001,11 +1004,11 @@
       <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -1024,11 +1027,11 @@
       <c r="E4" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4">
         <v>2</v>
@@ -1047,10 +1050,10 @@
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
     </row>
@@ -1068,27 +1071,27 @@
         <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3"/>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="6">
+      <c r="I7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="5">
         <v>6</v>
       </c>
     </row>
@@ -1100,15 +1103,15 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="6">
+      <c r="I8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="5">
         <v>6</v>
       </c>
     </row>
@@ -1120,7 +1123,7 @@
         <v>2</v>
       </c>
       <c r="I9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -1135,10 +1138,10 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1183,7 +1186,7 @@
         <v>10</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1219,16 +1222,16 @@
       <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>4</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="4">
         <v>18</v>
       </c>
     </row>
@@ -1242,13 +1245,13 @@
       <c r="E4" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="F4" s="10">
+        <v>2</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="5">
         <v>2</v>
       </c>
     </row>
@@ -1265,10 +1268,10 @@
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="6">
+      <c r="I5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
     </row>
@@ -1285,18 +1288,18 @@
       <c r="F6">
         <v>8</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="5">
+      <c r="I6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="4">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="4"/>
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3"/>
       <c r="E7" t="s">
         <v>9</v>
       </c>
@@ -1304,7 +1307,7 @@
         <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1318,15 +1321,15 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="6">
+      <c r="I8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="5">
         <v>6</v>
       </c>
     </row>
@@ -1337,10 +1340,10 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="6">
+      <c r="I9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="5">
         <v>6</v>
       </c>
     </row>
@@ -1348,23 +1351,23 @@
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>6</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" s="5">
+      <c r="I10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="4">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="4"/>
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3"/>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -1393,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16D6BA52-D251-4C79-9178-9127F1D4E27D}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" customWidth="1"/>
@@ -1409,7 +1412,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1417,24 +1420,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -1442,13 +1445,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -1456,13 +1459,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>26</v>
+      <c r="C6" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="D6">
         <v>100</v>
@@ -1470,13 +1473,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="D7">
         <v>100</v>
@@ -1484,13 +1487,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="D8">
         <v>100</v>
@@ -1498,13 +1501,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>100</v>
@@ -1512,7 +1515,7 @@
     </row>
     <row r="11" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1520,24 +1523,24 @@
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>100</v>
@@ -1545,13 +1548,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>32</v>
       </c>
       <c r="D15">
         <v>100</v>
@@ -1559,13 +1562,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
-        <v>35</v>
-      </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16">
         <v>30</v>
@@ -1573,13 +1576,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -1587,63 +1590,105 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
-        <v>39</v>
-      </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+    <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
         <v>49</v>
       </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>37</v>
+      <c r="D25">
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26">
         <v>50</v>
-      </c>
-      <c r="C26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26">
-        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1651,52 +1696,52 @@
         <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D28">
-        <v>30</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D29">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D30">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
         <v>54</v>
       </c>
-      <c r="B31" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" t="s">
-        <v>41</v>
+      <c r="C31" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D31">
         <v>100</v>
@@ -1704,13 +1749,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" t="s">
-        <v>41</v>
+        <v>54</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D32">
         <v>100</v>
@@ -1718,13 +1763,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>32</v>
+        <v>54</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D33">
         <v>100</v>
@@ -1732,13 +1777,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>32</v>
+        <v>54</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
       </c>
       <c r="D34">
         <v>100</v>
@@ -1746,13 +1791,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" t="s">
-        <v>32</v>
+        <v>54</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D35">
         <v>100</v>
@@ -1760,13 +1805,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>32</v>
+        <v>54</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D36">
         <v>100</v>
@@ -1774,13 +1819,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>32</v>
+        <v>54</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D37">
         <v>100</v>
@@ -1788,13 +1833,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
-      </c>
-      <c r="C38" t="s">
-        <v>32</v>
+        <v>54</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -1802,12 +1847,12 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D39">
@@ -1816,97 +1861,60 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D40">
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" t="s">
-        <v>25</v>
-      </c>
-      <c r="D41">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>66</v>
-      </c>
-      <c r="B42" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>67</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43">
-        <v>100</v>
+    <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>68</v>
-      </c>
-      <c r="B44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C44" t="s">
-        <v>26</v>
-      </c>
-      <c r="D44">
-        <v>100</v>
+      <c r="A44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>26</v>
+        <v>49</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
       </c>
       <c r="D45">
-        <v>100</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>26</v>
+        <v>77</v>
+      </c>
+      <c r="C46" t="s">
+        <v>24</v>
       </c>
       <c r="D46">
         <v>100</v>
@@ -1914,13 +1922,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D47">
         <v>100</v>
@@ -1928,13 +1936,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>26</v>
+        <v>54</v>
+      </c>
+      <c r="C48" t="s">
+        <v>31</v>
       </c>
       <c r="D48">
         <v>100</v>
@@ -1942,13 +1950,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>26</v>
+        <v>54</v>
+      </c>
+      <c r="C49" t="s">
+        <v>24</v>
       </c>
       <c r="D49">
         <v>100</v>
@@ -1956,62 +1964,57 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D50">
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>76</v>
-      </c>
-      <c r="B55" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" t="s">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" t="s">
         <v>25</v>
       </c>
-      <c r="D55">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="D51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" t="s">
         <v>25</v>
       </c>
-      <c r="D56">
+      <c r="D52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="9">
         <v>100</v>
       </c>
     </row>
